--- a/artfynd/A 18546-2024 artfynd.xlsx
+++ b/artfynd/A 18546-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123419352</v>
+        <v>123419354</v>
       </c>
       <c r="B2" t="n">
-        <v>57497</v>
+        <v>94987</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>210</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -713,16 +713,21 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Dåbo, Hls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>599974</v>
+        <v>599973</v>
       </c>
       <c r="R2" t="n">
-        <v>6790754</v>
+        <v>6790756</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -749,7 +754,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>2024_2287</t>
+          <t>2024_2283</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -759,7 +764,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,12 +774,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:46</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Födosök</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -805,10 +805,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123419354</v>
+        <v>123419352</v>
       </c>
       <c r="B3" t="n">
-        <v>94985</v>
+        <v>57497</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,25 +817,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>210</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -843,21 +843,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Dåbo, Hls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>599973</v>
+        <v>599974</v>
       </c>
       <c r="R3" t="n">
-        <v>6790756</v>
+        <v>6790754</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,7 +879,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2024_2283</t>
+          <t>2024_2287</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -894,7 +889,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +899,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:46</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Födosök</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 18546-2024 artfynd.xlsx
+++ b/artfynd/A 18546-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123419354</v>
       </c>
       <c r="B2" t="n">
-        <v>94987</v>
+        <v>94993</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 18546-2024 artfynd.xlsx
+++ b/artfynd/A 18546-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123419354</v>
       </c>
       <c r="B2" t="n">
-        <v>94996</v>
+        <v>95013</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -808,7 +808,7 @@
         <v>123419352</v>
       </c>
       <c r="B3" t="n">
-        <v>57497</v>
+        <v>57503</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 18546-2024 artfynd.xlsx
+++ b/artfynd/A 18546-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123419354</v>
       </c>
       <c r="B2" t="n">
-        <v>95013</v>
+        <v>95019</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -808,7 +808,7 @@
         <v>123419352</v>
       </c>
       <c r="B3" t="n">
-        <v>57503</v>
+        <v>57506</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 18546-2024 artfynd.xlsx
+++ b/artfynd/A 18546-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123419354</v>
       </c>
       <c r="B2" t="n">
-        <v>95019</v>
+        <v>95021</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -808,7 +808,7 @@
         <v>123419352</v>
       </c>
       <c r="B3" t="n">
-        <v>57506</v>
+        <v>57507</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 18546-2024 artfynd.xlsx
+++ b/artfynd/A 18546-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123419354</v>
       </c>
       <c r="B2" t="n">
-        <v>95021</v>
+        <v>95529</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 18546-2024 artfynd.xlsx
+++ b/artfynd/A 18546-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123419354</v>
+        <v>123419352</v>
       </c>
       <c r="B2" t="n">
-        <v>95529</v>
+        <v>57507</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>210</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -713,21 +713,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Dåbo, Hls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>599973</v>
+        <v>599974</v>
       </c>
       <c r="R2" t="n">
-        <v>6790756</v>
+        <v>6790754</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,7 +749,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>2024_2283</t>
+          <t>2024_2287</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -764,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,7 +769,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:46</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Födosök</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -805,10 +805,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123419352</v>
+        <v>123419354</v>
       </c>
       <c r="B3" t="n">
-        <v>57507</v>
+        <v>95529</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,25 +817,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>210</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -843,16 +843,21 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Dåbo, Hls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>599974</v>
+        <v>599973</v>
       </c>
       <c r="R3" t="n">
-        <v>6790754</v>
+        <v>6790756</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,7 +884,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2024_2287</t>
+          <t>2024_2283</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -889,7 +894,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -899,12 +904,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:46</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Födosök</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 18546-2024 artfynd.xlsx
+++ b/artfynd/A 18546-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123419352</v>
+        <v>123419354</v>
       </c>
       <c r="B2" t="n">
-        <v>57507</v>
+        <v>95529</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>210</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -713,16 +713,21 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Dåbo, Hls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>599974</v>
+        <v>599973</v>
       </c>
       <c r="R2" t="n">
-        <v>6790754</v>
+        <v>6790756</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -749,7 +754,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>2024_2287</t>
+          <t>2024_2283</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -759,7 +764,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,12 +774,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:46</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Födosök</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -805,10 +805,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123419354</v>
+        <v>123419352</v>
       </c>
       <c r="B3" t="n">
-        <v>95529</v>
+        <v>57507</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,25 +817,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>210</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -843,21 +843,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Dåbo, Hls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>599973</v>
+        <v>599974</v>
       </c>
       <c r="R3" t="n">
-        <v>6790756</v>
+        <v>6790754</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,7 +879,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2024_2283</t>
+          <t>2024_2287</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -894,7 +889,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +899,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:46</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Födosök</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 18546-2024 artfynd.xlsx
+++ b/artfynd/A 18546-2024 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>123419354</v>
       </c>
       <c r="B2" t="n">
-        <v>95551</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96554</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -808,16 +803,11 @@
         <v>123419352</v>
       </c>
       <c r="B3" t="n">
-        <v>57529</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">

--- a/artfynd/A 18546-2024 artfynd.xlsx
+++ b/artfynd/A 18546-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -797,6 +802,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123419354</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -922,8 +932,17 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123419352</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>